--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T08:45:50+00:00</t>
+    <t>2026-09-14T09:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:32:54+00:00</t>
+    <t>2026-09-15T09:11:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T09:11:17+00:00</t>
+    <t>2026-09-16T09:03:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:03:59+00:00</t>
+    <t>2026-09-18T08:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:45:46+00:00</t>
+    <t>2026-09-19T08:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-19T08:31:43+00:00</t>
+    <t>2026-09-20T09:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T09:02:38+00:00</t>
+    <t>2026-09-21T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T09:33:49+00:00</t>
+    <t>2026-09-22T09:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T09:02:23+00:00</t>
+    <t>2026-09-23T09:05:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:05:06+00:00</t>
+    <t>2026-09-26T09:04:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-26T09:04:06+00:00</t>
+    <t>2026-09-27T09:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-27T09:48:22+00:00</t>
+    <t>2026-09-28T10:08:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:08:08+00:00</t>
+    <t>2026-09-28T10:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:29:09+00:00</t>
+    <t>2026-09-29T10:23:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:23:21+00:00</t>
+    <t>2026-09-30T10:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:15:24+00:00</t>
+    <t>2026-10-01T10:44:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T10:44:11+00:00</t>
+    <t>2026-10-03T09:39:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-03T09:39:13+00:00</t>
+    <t>2026-10-04T10:24:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-04T10:24:59+00:00</t>
+    <t>2026-10-05T11:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T11:08:35+00:00</t>
+    <t>2026-10-06T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T11:03:00+00:00</t>
+    <t>2026-10-07T10:51:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T10:51:41+00:00</t>
+    <t>2026-10-08T11:09:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T11:09:48+00:00</t>
+    <t>2026-10-09T11:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T11:08:13+00:00</t>
+    <t>2026-10-10T10:26:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-10T10:26:06+00:00</t>
+    <t>2026-10-11T10:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T10:34:50+00:00</t>
+    <t>2026-10-12T11:38:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T11:38:18+00:00</t>
+    <t>2026-10-13T11:24:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T11:24:48+00:00</t>
+    <t>2026-10-14T09:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T09:16:31+00:00</t>
+    <t>2026-10-16T08:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:44:55+00:00</t>
+    <t>2026-10-17T08:16:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T08:16:30+00:00</t>
+    <t>2026-10-18T08:33:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:33:19+00:00</t>
+    <t>2026-10-19T09:34:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T09:34:29+00:00</t>
+    <t>2026-10-21T09:08:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:08:03+00:00</t>
+    <t>2026-10-22T09:10:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:10:10+00:00</t>
+    <t>2026-10-23T09:04:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:04:39+00:00</t>
+    <t>2026-10-24T08:37:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-24T08:37:27+00:00</t>
+    <t>2026-10-25T08:56:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-25T08:56:52+00:00</t>
+    <t>2026-10-26T09:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T09:38:46+00:00</t>
+    <t>2026-10-27T09:35:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T09:35:46+00:00</t>
+    <t>2026-10-28T10:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:20:37+00:00</t>
+    <t>2026-10-29T10:44:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:44:18+00:00</t>
+    <t>2026-10-30T10:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/main/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T10:44:55+00:00</t>
+    <t>2026-10-31T10:10:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
